--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
@@ -413,38 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Distance 1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Distance 2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Area</t>
         </is>
       </c>
     </row>
@@ -456,26 +446,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Fiducial 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.15413</v>
+        <v>125.67741</v>
       </c>
       <c r="D2" t="n">
-        <v>17.04595</v>
+        <v>87.78731000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01805</v>
+        <v>94.25686</v>
       </c>
       <c r="F2" t="n">
-        <v>43.76619</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.05224</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.88131</v>
+        <v>534.1672</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +469,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.12607</v>
+        <v>124.83458</v>
       </c>
       <c r="D3" t="n">
-        <v>16.94777</v>
+        <v>89.38533</v>
       </c>
       <c r="E3" t="n">
-        <v>17.27663</v>
+        <v>92.81068999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>43.37184</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.05187</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.85715</v>
+        <v>520.91958</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +488,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.07727</v>
+        <v>126.44182</v>
       </c>
       <c r="D4" t="n">
-        <v>17.1858</v>
+        <v>89.07691</v>
       </c>
       <c r="E4" t="n">
-        <v>17.316</v>
+        <v>92.51494</v>
       </c>
       <c r="F4" t="n">
-        <v>43.68079</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05217</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.86762</v>
+        <v>525.21591</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +507,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.57537</v>
+        <v>125.23332</v>
       </c>
       <c r="D5" t="n">
-        <v>17.23482</v>
+        <v>89.6746</v>
       </c>
       <c r="E5" t="n">
-        <v>17.1032</v>
+        <v>92.69459999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>44.16664</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.05282</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.86275</v>
+        <v>529.6838</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +525,17 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>125.83599</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86.46423</v>
+      </c>
+      <c r="E6" t="n">
+        <v>95.40081000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>525.23249</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +545,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.35985</v>
+        <v>124.55223</v>
       </c>
       <c r="D7" t="n">
-        <v>16.82351</v>
+        <v>89.62260000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>17.47427</v>
+        <v>92.53452</v>
       </c>
       <c r="F7" t="n">
-        <v>43.28891</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.05135</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.90471</v>
+        <v>538.82663</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +564,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.28715</v>
+        <v>124.89067</v>
       </c>
       <c r="D8" t="n">
-        <v>17.17649</v>
+        <v>87.82608</v>
       </c>
       <c r="E8" t="n">
-        <v>17.19869</v>
+        <v>95.37705</v>
       </c>
       <c r="F8" t="n">
-        <v>43.98523</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.05082</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.86444</v>
+        <v>544.38335</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +583,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.19496</v>
+        <v>124.0193</v>
       </c>
       <c r="D9" t="n">
-        <v>17.1337</v>
+        <v>87.5351</v>
       </c>
       <c r="E9" t="n">
-        <v>16.94041</v>
+        <v>90.84241</v>
       </c>
       <c r="F9" t="n">
-        <v>44.31562</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.05252</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.90923</v>
+        <v>536.25516</v>
       </c>
     </row>
     <row r="10">
@@ -647,48 +602,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.42734</v>
+        <v>125.42631</v>
       </c>
       <c r="D10" t="n">
-        <v>16.94737</v>
+        <v>88.42807000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>16.98527</v>
+        <v>94.43658000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>44.34534</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.05269</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.88137</v>
+        <v>530.63289</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Diameter</t>
         </is>
       </c>
     </row>
@@ -700,23 +634,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Micro Bump 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.3829</v>
+        <v>8.818770000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>16.59851</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.83778</v>
-      </c>
-      <c r="F12" t="n">
-        <v>22.70419</v>
-      </c>
-      <c r="G12" t="n">
-        <v>35.13747</v>
+        <v>24.88574</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +651,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.30933</v>
+        <v>8.8103</v>
       </c>
       <c r="D13" t="n">
-        <v>16.48079</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.41045</v>
-      </c>
-      <c r="F13" t="n">
-        <v>22.30243</v>
-      </c>
-      <c r="G13" t="n">
-        <v>35.08983</v>
+        <v>24.96714</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +663,11 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>17.15458</v>
+        <v>8.74837</v>
       </c>
       <c r="D14" t="n">
-        <v>16.52026</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.83493</v>
-      </c>
-      <c r="F14" t="n">
-        <v>22.32879</v>
-      </c>
-      <c r="G14" t="n">
-        <v>35.24547</v>
+        <v>24.68557</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +677,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.52574</v>
+        <v>8.95341</v>
       </c>
       <c r="D15" t="n">
-        <v>16.52259</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.78384</v>
-      </c>
-      <c r="F15" t="n">
-        <v>22.12943</v>
-      </c>
-      <c r="G15" t="n">
-        <v>35.3421</v>
+        <v>24.99398</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +690,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.15765</v>
+        <v>8.809749999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>16.5505</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.46199</v>
-      </c>
-      <c r="F16" t="n">
-        <v>21.94162</v>
-      </c>
-      <c r="G16" t="n">
-        <v>35.156</v>
+        <v>24.66545</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +703,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.41776</v>
+        <v>8.841559999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>16.47423</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.74129</v>
-      </c>
-      <c r="F17" t="n">
-        <v>22.6615</v>
-      </c>
-      <c r="G17" t="n">
-        <v>34.8446</v>
+        <v>25.23686</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +716,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.83244</v>
+        <v>9.01872</v>
       </c>
       <c r="D18" t="n">
-        <v>16.16519</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.14287</v>
-      </c>
-      <c r="F18" t="n">
-        <v>22.30478</v>
-      </c>
-      <c r="G18" t="n">
-        <v>34.93596</v>
+        <v>25.26841</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +729,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.76282</v>
+        <v>8.890319999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>16.64128</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.77431</v>
-      </c>
-      <c r="F19" t="n">
-        <v>22.43754</v>
-      </c>
-      <c r="G19" t="n">
-        <v>35.42668</v>
+        <v>24.68301</v>
       </c>
     </row>
     <row r="20">
@@ -885,60 +742,41 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.21231</v>
+        <v>8.948779999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>16.18668</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.9084</v>
-      </c>
-      <c r="F20" t="n">
-        <v>22.42008</v>
-      </c>
-      <c r="G20" t="n">
-        <v>35.5903</v>
+        <v>25.18866</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ra mean</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -950,32 +788,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.77537</v>
+        <v>17.24282</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08425000000000001</v>
+        <v>16.97604</v>
       </c>
       <c r="E22" t="n">
-        <v>0.62968</v>
+        <v>16.98409</v>
       </c>
       <c r="F22" t="n">
-        <v>0.99442</v>
+        <v>43.71059</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11321</v>
+        <v>0.05215</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09859999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12782</v>
+        <v>1.85702</v>
       </c>
     </row>
     <row r="23">
@@ -985,28 +817,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7665999999999999</v>
+        <v>17.3061</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08361</v>
+        <v>17.09039</v>
       </c>
       <c r="E23" t="n">
-        <v>0.63739</v>
+        <v>17.1789</v>
       </c>
       <c r="F23" t="n">
-        <v>0.99686</v>
+        <v>44.10848</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11337</v>
+        <v>0.05288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09514</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13022</v>
+        <v>1.91847</v>
       </c>
     </row>
     <row r="24">
@@ -1016,28 +842,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75892</v>
+        <v>17.52441</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08369</v>
+        <v>17.03312</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6244499999999999</v>
+        <v>17.11773</v>
       </c>
       <c r="F24" t="n">
-        <v>0.98292</v>
+        <v>43.41497</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11397</v>
+        <v>0.05341</v>
       </c>
       <c r="H24" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09549000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.13039</v>
+        <v>1.88101</v>
       </c>
     </row>
     <row r="25">
@@ -1047,28 +867,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.78988</v>
+        <v>17.64334</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08402999999999999</v>
+        <v>17.09543</v>
       </c>
       <c r="E25" t="n">
-        <v>0.63044</v>
+        <v>17.19603</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99698</v>
+        <v>43.26571</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11298</v>
+        <v>0.05171</v>
       </c>
       <c r="H25" t="n">
-        <v>0.007820000000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09754</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.1319</v>
+        <v>1.87838</v>
       </c>
     </row>
     <row r="26">
@@ -1078,28 +892,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.76092</v>
+        <v>17.58121</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08399</v>
+        <v>17.22128</v>
       </c>
       <c r="E26" t="n">
-        <v>0.62671</v>
+        <v>17.28826</v>
       </c>
       <c r="F26" t="n">
-        <v>0.98941</v>
+        <v>42.77807</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11216</v>
+        <v>0.05202</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00769</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09457</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.1311</v>
+        <v>1.91273</v>
       </c>
     </row>
     <row r="27">
@@ -1109,28 +917,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.77125</v>
+        <v>17.24078</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08136</v>
+        <v>17.03603</v>
       </c>
       <c r="E27" t="n">
-        <v>0.62762</v>
+        <v>17.22255</v>
       </c>
       <c r="F27" t="n">
-        <v>1.00084</v>
+        <v>43.53312</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11207</v>
+        <v>0.05155</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00766</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09437</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12962</v>
+        <v>1.8703</v>
       </c>
     </row>
     <row r="28">
@@ -1140,28 +942,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76272</v>
+        <v>17.45639</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08227</v>
+        <v>16.86482</v>
       </c>
       <c r="E28" t="n">
-        <v>0.62829</v>
+        <v>16.99875</v>
       </c>
       <c r="F28" t="n">
-        <v>0.98876</v>
+        <v>43.50262</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11379</v>
+        <v>0.05154</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00783</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09753000000000001</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13041</v>
+        <v>1.84431</v>
       </c>
     </row>
     <row r="29">
@@ -1171,28 +967,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.76661</v>
+        <v>17.33149</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08376</v>
+        <v>17.07821</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62746</v>
+        <v>17.2613</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9989</v>
+        <v>43.46568</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11345</v>
+        <v>0.0528</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00788</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09802</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12927</v>
+        <v>1.8353</v>
       </c>
     </row>
     <row r="30">
@@ -1202,28 +992,348 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.77383</v>
+        <v>17.19494</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08229</v>
+        <v>16.80366</v>
       </c>
       <c r="E30" t="n">
-        <v>0.61351</v>
+        <v>17.15311</v>
       </c>
       <c r="F30" t="n">
-        <v>0.98717</v>
+        <v>44.01221</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11256</v>
+        <v>0.05314</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00779</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09428</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13145</v>
+        <v>1.87024</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.76864</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08344</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.62108</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.99726</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11043</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09493</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.13015</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.75629</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08357000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.61513</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.99985</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11106</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09684</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12982</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7696</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08467</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.61516</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.00243</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11485</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09482</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.13141</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.74576</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08377999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6253300000000001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.98482</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11243</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00791</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12783</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7626500000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08169</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6469200000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.99257</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11251</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09735000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.13195</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.76417</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08251</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.62331</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.96572</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11179</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00791</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09675</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12972</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.78632</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08377</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6217</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.99888</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11291</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09671</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12724</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.78193</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08252</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.62709</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.99915</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11171</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09648</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.13396</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.77976</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08215</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.64168</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.96171</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.10829</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12901</v>
       </c>
     </row>
   </sheetData>
